--- a/notebooks/extra_tables/ema_rwd_final_statistics_tables_logit_vif_formatted.xlsx
+++ b/notebooks/extra_tables/ema_rwd_final_statistics_tables_logit_vif_formatted.xlsx
@@ -607,19 +607,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.072582580534232</v>
+        <v>1.07</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0151500723723</v>
+        <v>2.02</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8272108017543004</v>
+        <v>0.83</v>
       </c>
       <c r="I4" t="n">
-        <v>1.208881699657764</v>
+        <v>1.21</v>
       </c>
       <c r="J4" t="n">
         <v>68</v>
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.073239868827368</v>
+        <v>1.07</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.027533203901888</v>
+        <v>2.03</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8391268303418922</v>
+        <v>0.84</v>
       </c>
       <c r="P4" t="n">
-        <v>1.191714963508629</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="5">
@@ -661,19 +661,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.072582580534232</v>
+        <v>1.07</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0151500723723</v>
+        <v>2.02</v>
       </c>
       <c r="H5" t="n">
-        <v>0.919101502837118</v>
+        <v>0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>1.088019110961261</v>
+        <v>1.09</v>
       </c>
       <c r="J5" t="n">
         <v>19</v>
@@ -684,19 +684,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.073239868827368</v>
+        <v>1.07</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>2.027533203901888</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9489935190661432</v>
+        <v>0.95</v>
       </c>
       <c r="P5" t="n">
-        <v>1.053747976049457</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="6">
@@ -715,19 +715,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.072582580534232</v>
+        <v>1.07</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0151500723723</v>
+        <v>2.02</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6674579935868298</v>
+        <v>0.67</v>
       </c>
       <c r="I6" t="n">
-        <v>1.498221625343243</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>401</v>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.073239868827368</v>
+        <v>1.07</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.027533203901888</v>
+        <v>2.03</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6780679714926621</v>
+        <v>0.68</v>
       </c>
       <c r="P6" t="n">
-        <v>1.474778402818016</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="7">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.072582580534232</v>
+        <v>1.07</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0151500723723</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8812417191474186</v>
+        <v>0.88</v>
       </c>
       <c r="I7" t="n">
-        <v>1.134762436085615</v>
+        <v>1.13</v>
       </c>
       <c r="J7" t="n">
         <v>81</v>
@@ -792,19 +792,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.073239868827368</v>
+        <v>1.07</v>
       </c>
       <c r="M7" t="n">
         <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.027533203901888</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8724157135503368</v>
+        <v>0.87</v>
       </c>
       <c r="P7" t="n">
-        <v>1.146242536061682</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="8">
@@ -823,19 +823,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.072582580534232</v>
+        <v>1.07</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0151500723723</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8230747894336256</v>
+        <v>0.82</v>
       </c>
       <c r="I8" t="n">
-        <v>1.214956420531505</v>
+        <v>1.21</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -846,19 +846,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.073239868827368</v>
+        <v>1.07</v>
       </c>
       <c r="M8" t="n">
         <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.027533203901888</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8132176496869061</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>1.229683099456838</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="9">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.117159217367746</v>
+        <v>1.12</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.426166405668426</v>
+        <v>2.43</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6139975456647532</v>
+        <v>0.61</v>
       </c>
       <c r="I9" t="n">
-        <v>1.628671005382173</v>
+        <v>1.63</v>
       </c>
       <c r="J9" t="n">
         <v>246</v>
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.134157542232404</v>
+        <v>1.13</v>
       </c>
       <c r="M9" t="n">
         <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.737707727065248</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5838007054517281</v>
+        <v>0.58</v>
       </c>
       <c r="P9" t="n">
-        <v>1.712913312131456</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="10">
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.117159217367746</v>
+        <v>1.12</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>2.426166405668426</v>
+        <v>2.43</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7421209561872248</v>
+        <v>0.74</v>
       </c>
       <c r="I10" t="n">
-        <v>1.347489235633061</v>
+        <v>1.35</v>
       </c>
       <c r="J10" t="n">
         <v>40</v>
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.134157542232404</v>
+        <v>1.13</v>
       </c>
       <c r="M10" t="n">
         <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.737707727065248</v>
+        <v>2.74</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7024536695972079</v>
+        <v>0.7</v>
       </c>
       <c r="P10" t="n">
-        <v>1.423581430748888</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="11">
@@ -989,19 +989,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.117159217367746</v>
+        <v>1.12</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>2.426166405668426</v>
+        <v>2.43</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9080840131285497</v>
+        <v>0.91</v>
       </c>
       <c r="I11" t="n">
-        <v>1.101219695031057</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
         <v>22</v>
@@ -1012,19 +1012,19 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.134157542232404</v>
+        <v>1.13</v>
       </c>
       <c r="M11" t="n">
         <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.737707727065248</v>
+        <v>2.74</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8975816164401061</v>
+        <v>0.9</v>
       </c>
       <c r="P11" t="n">
-        <v>1.114104814185138</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="12">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.117159217367746</v>
+        <v>1.12</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>2.426166405668426</v>
+        <v>2.43</v>
       </c>
       <c r="H12" t="n">
-        <v>0.937927365847562</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1.066180640860549</v>
+        <v>1.07</v>
       </c>
       <c r="J12" t="n">
         <v>14</v>
@@ -1066,19 +1066,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.134157542232404</v>
+        <v>1.13</v>
       </c>
       <c r="M12" t="n">
         <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.737707727065248</v>
+        <v>2.74</v>
       </c>
       <c r="O12" t="n">
-        <v>0.95020059667357</v>
+        <v>0.95</v>
       </c>
       <c r="P12" t="n">
-        <v>1.05240935808793</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="13">
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.156362727783047</v>
+        <v>1.16</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1.33717475820585</v>
+        <v>1.34</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7473354834681465</v>
+        <v>0.75</v>
       </c>
       <c r="I13" t="n">
-        <v>1.338087140408907</v>
+        <v>1.34</v>
       </c>
       <c r="J13" t="n">
         <v>135</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.175928788866047</v>
+        <v>1.18</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>1.382808516483968</v>
+        <v>1.38</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7230620646304181</v>
+        <v>0.72</v>
       </c>
       <c r="P13" t="n">
-        <v>1.383007142701</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="14">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.07163249087097</v>
+        <v>1.07</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>1.514520775534277</v>
+        <v>1.51</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5591420206054732</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.788454387522402</v>
+        <v>1.79</v>
       </c>
       <c r="J14" t="n">
         <v>373</v>
@@ -1182,19 +1182,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.09332342734018</v>
+        <v>1.09</v>
       </c>
       <c r="M14" t="n">
         <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.708015960647026</v>
+        <v>1.71</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5412699475350268</v>
+        <v>0.54</v>
       </c>
       <c r="P14" t="n">
-        <v>1.847506968665183</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="15">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.07163249087097</v>
+        <v>1.07</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>1.514520775534277</v>
+        <v>1.51</v>
       </c>
       <c r="H15" t="n">
-        <v>0.540625424716542</v>
+        <v>0.54</v>
       </c>
       <c r="I15" t="n">
-        <v>1.849709529521878</v>
+        <v>1.85</v>
       </c>
       <c r="J15" t="n">
         <v>390</v>
@@ -1236,19 +1236,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.09332342734018</v>
+        <v>1.09</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>1.708015960647026</v>
+        <v>1.71</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4820857525943667</v>
+        <v>0.48</v>
       </c>
       <c r="P15" t="n">
-        <v>2.074319754563278</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="16">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.07163249087097</v>
+        <v>1.07</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.514520775534277</v>
+        <v>1.51</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5350804229037862</v>
+        <v>0.54</v>
       </c>
       <c r="I16" t="n">
-        <v>1.868877942820591</v>
+        <v>1.87</v>
       </c>
       <c r="J16" t="n">
         <v>393</v>
@@ -1290,19 +1290,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.09332342734018</v>
+        <v>1.09</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>1.708015960647026</v>
+        <v>1.71</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4637173731172342</v>
+        <v>0.46</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15648595021948</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="17">
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.130627998991962</v>
+        <v>1.13</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1.278319672104568</v>
+        <v>1.28</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7821205680347225</v>
+        <v>0.78</v>
       </c>
       <c r="I17" t="n">
-        <v>1.278575248970571</v>
+        <v>1.28</v>
       </c>
       <c r="J17" t="n">
         <v>577</v>
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.122930136478577</v>
+        <v>1.12</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.260972091411795</v>
+        <v>1.26</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7929086690946396</v>
+        <v>0.79</v>
       </c>
       <c r="P17" t="n">
-        <v>1.261179299681288</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="18">
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.032711815864797</v>
+        <v>1.03</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.13740880067865</v>
+        <v>1.14</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9325747493539489</v>
+        <v>0.93</v>
       </c>
       <c r="I18" t="n">
-        <v>1.07230010322793</v>
+        <v>1.07</v>
       </c>
       <c r="J18" t="n">
         <v>21</v>
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.043970871358167</v>
+        <v>1.04</v>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>1.187827908512611</v>
+        <v>1.19</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8982183418769152</v>
+        <v>0.9</v>
       </c>
       <c r="P18" t="n">
-        <v>1.113315052006622</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="19">
@@ -1437,19 +1437,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.032711815864797</v>
+        <v>1.03</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>1.13740880067865</v>
+        <v>1.14</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9402583200227908</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.063537518046914</v>
+        <v>1.06</v>
       </c>
       <c r="J19" t="n">
         <v>23</v>
@@ -1460,19 +1460,19 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.043970871358167</v>
+        <v>1.04</v>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>1.187827908512611</v>
+        <v>1.19</v>
       </c>
       <c r="O19" t="n">
-        <v>0.935523073034939</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>1.068920723415074</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="20">
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.065896422820478</v>
+        <v>1.07</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>1.666172789437331</v>
+        <v>1.67</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6870344670372789</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>1.45553105117467</v>
+        <v>1.46</v>
       </c>
       <c r="J20" t="n">
         <v>168</v>
@@ -1518,19 +1518,19 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.067974689275552</v>
+        <v>1.07</v>
       </c>
       <c r="M20" t="n">
         <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>1.692340240299077</v>
+        <v>1.69</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6714057495175845</v>
+        <v>0.67</v>
       </c>
       <c r="P20" t="n">
-        <v>1.489412327372108</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="21">
@@ -1549,19 +1549,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.065896422820478</v>
+        <v>1.07</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>1.666172789437331</v>
+        <v>1.67</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7352866087189864</v>
+        <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>1.360013888655196</v>
+        <v>1.36</v>
       </c>
       <c r="J21" t="n">
         <v>146</v>
@@ -1572,19 +1572,19 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.067974689275552</v>
+        <v>1.07</v>
       </c>
       <c r="M21" t="n">
         <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.692340240299077</v>
+        <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7394811290952037</v>
+        <v>0.74</v>
       </c>
       <c r="P21" t="n">
-        <v>1.352299552557285</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="22">
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.065896422820478</v>
+        <v>1.07</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>1.666172789437331</v>
+        <v>1.67</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5860589489362312</v>
+        <v>0.59</v>
       </c>
       <c r="I22" t="n">
-        <v>1.706312994307352</v>
+        <v>1.71</v>
       </c>
       <c r="J22" t="n">
         <v>347</v>
@@ -1626,19 +1626,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.067974689275552</v>
+        <v>1.07</v>
       </c>
       <c r="M22" t="n">
         <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.692340240299077</v>
+        <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5764737148956091</v>
+        <v>0.58</v>
       </c>
       <c r="P22" t="n">
-        <v>1.73468446897199</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="23">
@@ -1657,19 +1657,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.065896422820478</v>
+        <v>1.07</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>1.666172789437331</v>
+        <v>1.67</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4478223352204873</v>
+        <v>0.45</v>
       </c>
       <c r="I23" t="n">
-        <v>2.233028416297382</v>
+        <v>2.23</v>
       </c>
       <c r="J23" t="n">
         <v>501</v>
@@ -1680,19 +1680,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.067974689275552</v>
+        <v>1.07</v>
       </c>
       <c r="M23" t="n">
         <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.692340240299077</v>
+        <v>1.69</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4456101343568479</v>
+        <v>0.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.244114132285853</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="24">
@@ -1715,19 +1715,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.047125979413853</v>
+        <v>1.05</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>1.202252637901109</v>
+        <v>1.2</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9208564154930813</v>
+        <v>0.92</v>
       </c>
       <c r="I24" t="n">
-        <v>1.085945629715291</v>
+        <v>1.09</v>
       </c>
       <c r="J24" t="n">
         <v>99</v>
@@ -1738,19 +1738,19 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.061291630104257</v>
+        <v>1.06</v>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>1.268641624687713</v>
+        <v>1.27</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9003272470899936</v>
+        <v>0.9</v>
       </c>
       <c r="P24" t="n">
-        <v>1.110707249205403</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="25">
@@ -1769,19 +1769,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.047125979413853</v>
+        <v>1.05</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>1.202252637901109</v>
+        <v>1.2</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8360685567356473</v>
+        <v>0.84</v>
       </c>
       <c r="I25" t="n">
-        <v>1.196074163947043</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>428</v>
@@ -1792,19 +1792,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.061291630104257</v>
+        <v>1.06</v>
       </c>
       <c r="M25" t="n">
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>1.268641624687713</v>
+        <v>1.27</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8060020732672145</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>1.240691597661026</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="26">
@@ -1827,19 +1827,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.068963374996803</v>
+        <v>1.07</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1.142682697084556</v>
+        <v>1.14</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8750558059440814</v>
+        <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>1.142784258109251</v>
+        <v>1.14</v>
       </c>
       <c r="J26" t="n">
         <v>402</v>
@@ -1850,19 +1850,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.074031342553127</v>
+        <v>1.07</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.153543324786473</v>
+        <v>1.15</v>
       </c>
       <c r="O26" t="n">
-        <v>0.8668438356655089</v>
+        <v>0.87</v>
       </c>
       <c r="P26" t="n">
-        <v>1.153610326169375</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="27">
@@ -1885,19 +1885,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.059537897941724</v>
+        <v>1.06</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1.122620557174767</v>
+        <v>1.12</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8906970691041618</v>
+        <v>0.89</v>
       </c>
       <c r="I27" t="n">
-        <v>1.122716167692987</v>
+        <v>1.12</v>
       </c>
       <c r="J27" t="n">
         <v>1208</v>
@@ -1908,19 +1908,19 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.071451653064425</v>
+        <v>1.07</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1.148008644854489</v>
+        <v>1.15</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8709407167603517</v>
+        <v>0.87</v>
       </c>
       <c r="P27" t="n">
-        <v>1.148183775033175</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="28">
@@ -1943,19 +1943,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.090497665655317</v>
+        <v>1.09</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1.189185158799696</v>
+        <v>1.19</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8411323647642058</v>
+        <v>0.84</v>
       </c>
       <c r="I28" t="n">
-        <v>1.188873525607744</v>
+        <v>1.19</v>
       </c>
       <c r="J28" t="n">
         <v>144</v>
@@ -1966,19 +1966,19 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.079924649233619</v>
+        <v>1.08</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.166237248022355</v>
+        <v>1.17</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8577494723333011</v>
+        <v>0.86</v>
       </c>
       <c r="P28" t="n">
-        <v>1.165841579919298</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="29">
@@ -2001,19 +2001,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.173135608594766</v>
+        <v>1.17</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>1.376247156153012</v>
+        <v>1.38</v>
       </c>
       <c r="H29" t="n">
-        <v>0.727592396726763</v>
+        <v>0.73</v>
       </c>
       <c r="I29" t="n">
-        <v>1.374395890472088</v>
+        <v>1.37</v>
       </c>
       <c r="J29" t="n">
         <v>501</v>
@@ -2024,19 +2024,19 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.19066577219764</v>
+        <v>1.19</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.417684981083002</v>
+        <v>1.42</v>
       </c>
       <c r="O29" t="n">
-        <v>0.7076150207826309</v>
+        <v>0.71</v>
       </c>
       <c r="P29" t="n">
-        <v>1.41319781326008</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="30">
@@ -2059,19 +2059,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.18294602136324</v>
+        <v>1.18</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1.399361289459119</v>
+        <v>1.4</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7148273854095196</v>
+        <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>1.398939129097729</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -2101,19 +2101,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.07007998891346</v>
+        <v>1.07</v>
       </c>
       <c r="F31" t="n">
         <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>1.719214006452929</v>
+        <v>1.72</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5852085301513458</v>
+        <v>0.59</v>
       </c>
       <c r="I31" t="n">
-        <v>1.708792590124039</v>
+        <v>1.71</v>
       </c>
       <c r="J31" t="n">
         <v>293</v>
@@ -2124,19 +2124,19 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.041902387752062</v>
+        <v>1.04</v>
       </c>
       <c r="M31" t="n">
         <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>1.388725040670991</v>
+        <v>1.39</v>
       </c>
       <c r="O31" t="n">
-        <v>0.5927231306145548</v>
+        <v>0.59</v>
       </c>
       <c r="P31" t="n">
-        <v>1.68712835445306</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="32">
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.07007998891346</v>
+        <v>1.07</v>
       </c>
       <c r="F32" t="n">
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>1.719214006452929</v>
+        <v>1.72</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5520649792939719</v>
+        <v>0.55</v>
       </c>
       <c r="I32" t="n">
-        <v>1.811380974172435</v>
+        <v>1.81</v>
       </c>
       <c r="J32" t="n">
         <v>294</v>
@@ -2178,19 +2178,19 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.041902387752062</v>
+        <v>1.04</v>
       </c>
       <c r="M32" t="n">
         <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>1.388725040670991</v>
+        <v>1.39</v>
       </c>
       <c r="O32" t="n">
-        <v>0.5728838781309001</v>
+        <v>0.57</v>
       </c>
       <c r="P32" t="n">
-        <v>1.74555444510433</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="33">
@@ -2209,19 +2209,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.07007998891346</v>
+        <v>1.07</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>1.719214006452929</v>
+        <v>1.72</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4408184309222378</v>
+        <v>0.44</v>
       </c>
       <c r="I33" t="n">
-        <v>2.268507688999973</v>
+        <v>2.27</v>
       </c>
       <c r="J33" t="n">
         <v>295</v>
@@ -2232,19 +2232,19 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.041902387752062</v>
+        <v>1.04</v>
       </c>
       <c r="M33" t="n">
         <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>1.388725040670991</v>
+        <v>1.39</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5288897193527603</v>
+        <v>0.53</v>
       </c>
       <c r="P33" t="n">
-        <v>1.89075333365105</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="34">
@@ -2263,19 +2263,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.07007998891346</v>
+        <v>1.07</v>
       </c>
       <c r="F34" t="n">
         <v>4</v>
       </c>
       <c r="G34" t="n">
-        <v>1.719214006452929</v>
+        <v>1.72</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5168951378050163</v>
+        <v>0.52</v>
       </c>
       <c r="I34" t="n">
-        <v>1.934628374038258</v>
+        <v>1.93</v>
       </c>
       <c r="J34" t="n">
         <v>303</v>
@@ -2286,19 +2286,19 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.041902387752062</v>
+        <v>1.04</v>
       </c>
       <c r="M34" t="n">
         <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>1.388725040670991</v>
+        <v>1.39</v>
       </c>
       <c r="O34" t="n">
-        <v>0.5491412091659794</v>
+        <v>0.55</v>
       </c>
       <c r="P34" t="n">
-        <v>1.821025235965759</v>
+        <v>1.82</v>
       </c>
     </row>
   </sheetData>
